--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260826.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>16.87%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>3,150,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.79%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>3,100,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.71%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.85%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>1,087,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -809,56 +809,56 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,040,000</t>
+          <t>2,880,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>630,000</t>
+          <t>660,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>626,000</t>
+          <t>4,550,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,250,000</t>
+          <t>626,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>610,000</t>
+          <t>621,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>179,500</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>179,500</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1078,117 +1078,117 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,720,000</t>
+          <t>10,358,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,737,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,360,000</t>
+          <t>866,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>780,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1254,46 +1254,46 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1386,24 +1386,24 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>393,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>393,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>10,178,153,121</t>
+          <t>10,569,798,466</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>87,354,442</t>
+          <t>-479,094,741</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,737,461,838</t>
+          <t>5,457,566,030</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
